--- a/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
+++ b/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
+++ b/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
+++ b/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
+++ b/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="94">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,7 +250,7 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {valueset-reference}
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
@@ -258,6 +258,10 @@
   </si>
   <si>
     <t>SharedDataModelBiospecimenCollection.participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://nih-ncpi.github.io/ncpi-fhir-ig-2/StructureDefinition/ncpi-participant)
+</t>
   </si>
   <si>
     <t>The participant from whom the biospecimen was taken</t>
@@ -610,7 +614,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="25.94921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="68.5078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -975,13 +979,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1049,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1075,13 +1079,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1132,7 +1136,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>72</v>
@@ -1149,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1175,13 +1179,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1232,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>72</v>
@@ -1249,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1275,13 +1279,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1332,7 +1336,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>72</v>
@@ -1349,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1375,13 +1379,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1432,7 +1436,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>72</v>
@@ -1449,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1475,13 +1479,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1532,7 +1536,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>72</v>

--- a/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
+++ b/StructureDefinition-SharedDataModelBiospecimenCollection.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
